--- a/reference/reference_data.xlsx
+++ b/reference/reference_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\Important documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcg\Documents\PythonProject\Running_Analytics\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3703FC-CD52-402E-AE0C-A5060E7A1F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43A2FEE-C75C-411F-B3FB-4E6C471358CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Personal Bests" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
   <si>
     <t>Country</t>
   </si>
@@ -154,15 +154,9 @@
     <t>Hampshire 5.16km</t>
   </si>
   <si>
-    <t>Hampshire 6.42km</t>
-  </si>
-  <si>
     <t>Hampshire 6.56km</t>
   </si>
   <si>
-    <t>Ireland 6.92km</t>
-  </si>
-  <si>
     <t>Hampshire 7.29km</t>
   </si>
   <si>
@@ -172,9 +166,6 @@
     <t>Hampshire 7.58km</t>
   </si>
   <si>
-    <t>Hampshire 7.78km</t>
-  </si>
-  <si>
     <t>Ireland 8.29km</t>
   </si>
   <si>
@@ -212,6 +203,12 @@
   </si>
   <si>
     <t>Marathon</t>
+  </si>
+  <si>
+    <t>Hampshire 11.4km</t>
+  </si>
+  <si>
+    <t>Hampshire 14.86km</t>
   </si>
 </sst>
 </file>
@@ -553,7 +550,7 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -561,7 +558,7 @@
         <v>1.61</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -569,7 +566,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -577,7 +574,7 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -585,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -593,7 +590,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -601,7 +598,7 @@
         <v>21.1</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -609,7 +606,7 @@
         <v>42.2</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -619,7 +616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D6CF3E-0E01-4496-A843-30374E906243}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
@@ -650,7 +647,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>6.42</v>
+        <v>6.56</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -661,7 +658,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>6.56</v>
+        <v>7.29</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -672,7 +669,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>6.92</v>
+        <v>7.44</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -683,7 +680,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>7.29</v>
+        <v>7.58</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -694,7 +691,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>7.44</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -705,7 +702,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7.58</v>
+        <v>8.69</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -716,7 +713,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7.78</v>
+        <v>10.28</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -727,57 +724,46 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>8.2899999999999991</v>
+        <v>11.4</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>8.69</v>
+        <v>11.84</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10.28</v>
+        <v>12.8</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>11.84</v>
+        <v>14.86</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>12.8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
